--- a/registry/API_Registry_Correct.xlsx
+++ b/registry/API_Registry_Correct.xlsx
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +98,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -478,6 +481,7 @@
     <col width="35" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -546,6 +550,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Response Metrics</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -609,6 +618,11 @@
           <t>dateRange must be nested object {start, end}. ids=employee ID filter. userid=viewer (auto-injected). Default reportType=GROUP_REPORT</t>
         </is>
       </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data1.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data1.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data1.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data1.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data1.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -672,6 +686,11 @@
           <t>No specific employee required. Filter by org dimensions.</t>
         </is>
       </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data1.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data1.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data1.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data1.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data1.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -735,6 +754,11 @@
           <t>Same endpoint as activity summary. reportType=GROUP_REPORT</t>
         </is>
       </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data1.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data1.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data1.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data1.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data1.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -798,6 +822,11 @@
           <t>reportType should be WEEKLY_EXPORT</t>
         </is>
       </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data1.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data1.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data1.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data1.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data1.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -861,6 +890,11 @@
           <t>month=full name e.g. January. year=4-digit e.g. 2026. Both via GET query string.</t>
         </is>
       </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data12.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data12.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data12.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data12.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data12.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -924,6 +958,11 @@
           <t>Same endpoint as monthly_productivity_summary</t>
         </is>
       </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data12.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data12.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data12.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data12.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data12.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -983,6 +1022,11 @@
         </is>
       </c>
       <c r="M8" s="2" t="n"/>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data12.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data12.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data12.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data12.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data12.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1046,6 +1090,11 @@
           <t>ids=employee ID. month=January. year=2026</t>
         </is>
       </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data12.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data12.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data12.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data12.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data12.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1109,6 +1158,11 @@
           <t>All filter params are UPPERCASE arrays. userid=viewer auto-injected. Default reportType=SUMMARY_REPORT</t>
         </is>
       </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1168,6 +1222,11 @@
         </is>
       </c>
       <c r="M11" s="3" t="n"/>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1227,6 +1286,11 @@
         </is>
       </c>
       <c r="M12" s="2" t="n"/>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1286,6 +1350,11 @@
         </is>
       </c>
       <c r="M13" s="3" t="n"/>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1345,6 +1414,11 @@
         </is>
       </c>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1408,6 +1482,11 @@
           <t>selectedDepartments=array. EMPID=viewer (not filter). ids=employee filter.</t>
         </is>
       </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1471,6 +1550,11 @@
           <t>selectedTeams=array of team names</t>
         </is>
       </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1530,6 +1614,11 @@
         </is>
       </c>
       <c r="M17" s="3" t="n"/>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1593,6 +1682,11 @@
           <t>selectedShift=array of shift names</t>
         </is>
       </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -1652,6 +1746,11 @@
         </is>
       </c>
       <c r="M19" s="3" t="n"/>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Logged hours","matches":["logged hours","hours logged","logged time"],"path":"data.*.TotalLoggedHours","aggregation":"sum","format":"duration"},{"label":"Productive hours","matches":["productive hours","productive time"],"path":"data.*.TotalProductiveHours","aggregation":"sum","format":"duration"},{"label":"Idle hours","matches":["idle hours","idle time"],"path":"data.*.TotalIdleHours","aggregation":"sum","format":"duration"},{"label":"Time on system","matches":["time on system","on-system hours","on system hours"],"path":"data.*.TOTAL_ON_SYSTEM","aggregation":"sum","format":"duration"},{"label":"Time away from system","matches":["time away from system","away-from-system hours","away from system hours"],"path":"data.*.AwayFromSystem","aggregation":"sum","format":"duration"}]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -3211,6 +3310,11 @@
           <t>userid=scope auto-injected. Dates auto-calculated (current month vs last month). No date param needed.</t>
         </is>
       </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Last month efficiency","matches":["last month efficiency","previous month efficiency"],"path":"last_month.efficiency_percentage","aggregation":"first","format":"text","suffix":"%"},{"label":"Current month efficiency","matches":["current month efficiency","this month efficiency"],"path":"current_month.efficiency_percentage","aggregation":"first","format":"text","suffix":"%"},{"label":"Efficiency change","matches":["efficiency change percent","percentage efficiency change"],"path":"comparison.efficiency_change_percent","aggregation":"first","format":"text","suffix":"%"}]</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -3394,6 +3498,11 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>Fetches leave history without a date range; RAG returns the latest past APPROVED leave. userId is auto-injected.</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>[{"label":"Last approved leave ended","matches":["when did i last take leave","last leave date","last leave taken"],"path":"data.0.toDate","aggregation":"first","format":"text"}]</t>
         </is>
       </c>
     </row>
